--- a/noaa_mrip_survey_data_dictionary.xlsx
+++ b/noaa_mrip_survey_data_dictionary.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLopez.SOLIDIATECH\de_projects\noaa_eda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3C0D887-EC9B-482F-A358-8D788809E90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B3251C-DCEB-4E87-BFF2-A58CDD0914BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="-110" windowWidth="18020" windowHeight="12220" firstSheet="3"/>
+    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" tabRatio="787" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="size_begin2013w2" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="FES_Person" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">catch_begin2013w2!$A$1:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">size_begin2013w2!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">trip_begin2013w2!$A$1:$G$81</definedName>
     <definedName name="catch">catch_begin2013w2!$A$1:$F$36</definedName>
     <definedName name="catch_pre2013w2">catch_pre2013w2!$A$1:$F$30</definedName>
     <definedName name="size">size_begin2013w2!$A$1:$F$25</definedName>
@@ -31,17 +34,6 @@
     <definedName name="trip_pre2013w2">trip_pre2013w2!$A$1:$F$76</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1766,7 +1758,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
@@ -1821,12 +1813,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1866,25 +1870,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1893,46 +1897,233 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6B8B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2299,20 +2490,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="5" max="5" width="44.7265625" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="54.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="44.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="54.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -2335,78 +2526,77 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="C2" s="12">
-        <v>1</v>
-      </c>
-      <c r="D2" s="12">
-        <v>8</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="15" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="16" customFormat="1" ht="114.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C3" s="12">
-        <v>2</v>
-      </c>
-      <c r="D3" s="12">
-        <v>15</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="B3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="12">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="G4" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="5">
@@ -2422,55 +2612,52 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>252</v>
+      <c r="B6" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="C6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>151</v>
+      <c r="B7" s="25" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>247</v>
+        <v>83</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>124</v>
+      <c r="B8" s="25" t="s">
+        <v>194</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
@@ -2479,18 +2666,21 @@
         <v>8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>25</v>
+        <v>103</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
+      <c r="B9" s="25" t="s">
+        <v>285</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -2499,18 +2689,21 @@
         <v>8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>83</v>
+        <v>17</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>113</v>
+      <c r="B10" s="25" t="s">
+        <v>65</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
@@ -2519,21 +2712,21 @@
         <v>8</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>194</v>
+        <v>301</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -2542,242 +2735,237 @@
         <v>8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>105</v>
+        <v>302</v>
       </c>
       <c r="C12" s="5">
         <v>2</v>
       </c>
       <c r="D12" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
       </c>
       <c r="D13" s="5">
-        <v>2</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>312</v>
+        <v>30</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="C14" s="5">
         <v>2</v>
       </c>
       <c r="D14" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="C15" s="5">
         <v>2</v>
       </c>
       <c r="D15" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F15" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>116</v>
+        <v>303</v>
       </c>
       <c r="C16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>110</v>
+        <v>308</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>266</v>
+        <v>41</v>
       </c>
       <c r="C17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>296</v>
+      <c r="B18" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="C18" s="5">
         <v>2</v>
       </c>
       <c r="D18" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>29</v>
+        <v>286</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>244</v>
+      <c r="B19" s="19" t="s">
+        <v>252</v>
       </c>
       <c r="C19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>24</v>
+        <v>311</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>303</v>
+      <c r="B20" s="19" t="s">
+        <v>151</v>
       </c>
       <c r="C20" s="5">
         <v>2</v>
       </c>
       <c r="D20" s="5">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="F20" t="s">
-        <v>29</v>
+        <v>247</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>275</v>
+      <c r="B21" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="C21" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>274</v>
+        <v>78</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>285</v>
+      <c r="B22" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
@@ -2786,21 +2974,21 @@
         <v>8</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>17</v>
+        <v>279</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>65</v>
+      <c r="B23" s="19" t="s">
+        <v>244</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
@@ -2809,21 +2997,21 @@
         <v>8</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
+      <c r="B24" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
@@ -2832,17 +3020,20 @@
         <v>8</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>199</v>
+        <v>274</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="19" t="s">
         <v>217</v>
       </c>
       <c r="C25" s="5">
@@ -2862,6 +3053,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G25">
+      <sortCondition sortBy="cellColor" ref="B1:B25" dxfId="4"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -2869,20 +3065,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="5" max="5" width="43.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="54.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="54.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -2905,99 +3101,99 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="C2" s="12">
-        <v>1</v>
-      </c>
-      <c r="D2" s="12">
-        <v>8</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="15" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="16" customFormat="1" ht="114.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C3" s="12">
-        <v>2</v>
-      </c>
-      <c r="D3" s="12">
-        <v>15</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="12">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>112</v>
+      <c r="B5" s="20" t="s">
+        <v>235</v>
       </c>
       <c r="C5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>320</v>
+      <c r="B6" s="25" t="s">
+        <v>112</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -3006,64 +3202,58 @@
         <v>8</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>35</v>
+      <c r="B7" s="25" t="s">
+        <v>246</v>
       </c>
       <c r="C7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>242</v>
+      <c r="B8" s="25" t="s">
+        <v>173</v>
       </c>
       <c r="C8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>216</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>22</v>
+      <c r="B9" s="25" t="s">
+        <v>267</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -3072,18 +3262,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>323</v>
+      <c r="B10" s="25" t="s">
+        <v>87</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
@@ -3092,61 +3282,58 @@
         <v>8</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>252</v>
+      <c r="B11" s="25" t="s">
+        <v>206</v>
       </c>
       <c r="C11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>151</v>
+      <c r="B12" s="25" t="s">
+        <v>97</v>
       </c>
       <c r="C12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>268</v>
+      <c r="B13" s="25" t="s">
+        <v>84</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
@@ -3155,257 +3342,258 @@
         <v>8</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>49</v>
+      </c>
       <c r="G13" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>105</v>
+        <v>301</v>
       </c>
       <c r="C14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="C15" s="5">
         <v>2</v>
       </c>
       <c r="D15" s="5">
-        <v>2</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="5">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
         <v>30</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="25" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="5" t="s">
+    <row r="18" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="C18" s="5">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>110</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>8</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>325</v>
+        <v>266</v>
       </c>
       <c r="C19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="C20" s="5">
         <v>2</v>
       </c>
       <c r="D20" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>116</v>
+        <v>303</v>
       </c>
       <c r="C21" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>110</v>
+        <v>308</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="C22" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>296</v>
+        <v>61</v>
       </c>
       <c r="C23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>29</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F23" s="7"/>
       <c r="G23" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>244</v>
+      <c r="B24" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="C24" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>24</v>
+        <v>286</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>246</v>
+      <c r="B25" s="19" t="s">
+        <v>320</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
@@ -3414,18 +3602,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>173</v>
+      <c r="B26" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
@@ -3434,18 +3622,18 @@
         <v>8</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>267</v>
+      <c r="B27" s="19" t="s">
+        <v>323</v>
       </c>
       <c r="C27" s="5">
         <v>1</v>
@@ -3454,81 +3642,84 @@
         <v>8</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>87</v>
+      <c r="B28" s="19" t="s">
+        <v>252</v>
       </c>
       <c r="C28" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>118</v>
+        <v>311</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>303</v>
+      <c r="B29" s="19" t="s">
+        <v>151</v>
       </c>
       <c r="C29" s="5">
         <v>2</v>
       </c>
       <c r="D29" s="5">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="F29" t="s">
-        <v>29</v>
+        <v>247</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>275</v>
+      <c r="B30" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="C30" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>274</v>
+        <v>78</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>206</v>
+      <c r="B31" s="19" t="s">
+        <v>162</v>
       </c>
       <c r="C31" s="5">
         <v>1</v>
@@ -3537,18 +3728,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>234</v>
+        <v>153</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>97</v>
+      <c r="B32" s="19" t="s">
+        <v>325</v>
       </c>
       <c r="C32" s="5">
         <v>1</v>
@@ -3557,18 +3748,18 @@
         <v>8</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>84</v>
+      <c r="B33" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="C33" s="5">
         <v>1</v>
@@ -3577,18 +3768,21 @@
         <v>8</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>49</v>
+        <v>279</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="125" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>304</v>
+      <c r="B34" s="19" t="s">
+        <v>244</v>
       </c>
       <c r="C34" s="5">
         <v>1</v>
@@ -3597,18 +3791,21 @@
         <v>8</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>199</v>
+        <v>24</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>61</v>
+      <c r="B35" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="C35" s="5">
         <v>1</v>
@@ -3617,18 +3814,17 @@
         <v>8</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="7"/>
+        <v>274</v>
+      </c>
       <c r="G35" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="19" t="s">
         <v>217</v>
       </c>
       <c r="C36" s="5">
@@ -3645,6 +3841,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G36" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G36">
+      <sortCondition sortBy="cellColor" ref="B1:B36" dxfId="7"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -3652,21 +3853,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H81"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="5" max="5" width="48.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="48.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
     <col min="7" max="7" width="90" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -3690,488 +3891,486 @@
       </c>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="23"/>
+      <c r="G2" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="21">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21">
+        <v>8</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="21">
+        <v>1</v>
+      </c>
+      <c r="D6" s="21">
+        <v>8</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F6" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G6" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="5">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="25" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" ht="50" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="12" t="s">
+    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C5" s="12">
-        <v>1</v>
-      </c>
-      <c r="D5" s="12">
-        <v>8</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="15" t="s">
+      <c r="F8" s="5"/>
+      <c r="G8" s="13" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="16" customFormat="1" ht="77" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="12" t="s">
+    <row r="9" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C6" s="12">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
         <v>15</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E9" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G9" s="14" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="337.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="10" spans="1:8" ht="344.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="362.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="11" spans="1:8" ht="369.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="5">
-        <v>2</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F9" s="5" t="s">
+    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>13</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>25</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5">
+        <v>14</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="50" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>8</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5">
-        <v>13</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5">
-        <v>8</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="50" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
-        <v>8</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G20" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>8</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1</v>
-      </c>
-      <c r="D14" s="5">
-        <v>8</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="25" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>8</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="G21" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>8</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5">
-        <v>8</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="G22" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>8</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>8</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="5">
-        <v>2</v>
-      </c>
-      <c r="D20" s="5">
-        <v>25</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5">
-        <v>14</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="G23" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
@@ -4180,21 +4379,21 @@
         <v>8</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>93</v>
+        <v>281</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
@@ -4203,21 +4402,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>110</v>
+        <v>241</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
@@ -4226,44 +4422,42 @@
         <v>8</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>101</v>
+        <v>218</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>149</v>
+        <v>292</v>
       </c>
       <c r="C27" s="5">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>145</v>
+        <v>292</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>44</v>
+        <v>221</v>
       </c>
       <c r="C28" s="5">
         <v>1</v>
@@ -4272,21 +4466,21 @@
         <v>8</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="162.5" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="369.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
       <c r="C29" s="5">
         <v>1</v>
@@ -4295,42 +4489,43 @@
         <v>8</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>281</v>
+        <v>220</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>287</v>
+        <v>45</v>
       </c>
       <c r="C30" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>73</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F30" s="7"/>
       <c r="G30" s="6" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>280</v>
+        <v>172</v>
       </c>
       <c r="C31" s="5">
         <v>1</v>
@@ -4339,19 +4534,19 @@
         <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C32" s="5">
         <v>1</v>
@@ -4360,112 +4555,105 @@
         <v>8</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>8</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C34" s="5">
+        <v>2</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <v>8</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>8</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C33" s="5">
-        <v>2</v>
-      </c>
-      <c r="D33" s="5">
-        <v>16</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1</v>
-      </c>
-      <c r="D34" s="5">
-        <v>8</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="5">
-        <v>2</v>
-      </c>
-      <c r="D35" s="5">
-        <v>2</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="G36" s="6" t="s">
-        <v>293</v>
+        <v>120</v>
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="C37" s="5">
         <v>1</v>
@@ -4474,21 +4662,21 @@
         <v>8</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="362.5" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="C38" s="5">
         <v>1</v>
@@ -4497,88 +4685,87 @@
         <v>8</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>48</v>
+        <v>262</v>
       </c>
       <c r="C39" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F39" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>8</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="5">
+        <v>2</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="5">
-        <v>2</v>
-      </c>
-      <c r="D40" s="5">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="137.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="5">
-        <v>2</v>
-      </c>
-      <c r="D41" s="5">
-        <v>5</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F41" s="7"/>
       <c r="G41" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="C42" s="5">
         <v>1</v>
@@ -4587,142 +4774,154 @@
         <v>8</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>198</v>
+        <v>184</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="C43" s="5">
         <v>2</v>
       </c>
       <c r="D43" s="5">
-        <v>2</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>282</v>
+        <v>10</v>
       </c>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C44" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2</v>
+      </c>
+      <c r="D45" s="5">
+        <v>10</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5">
+        <v>2</v>
+      </c>
+      <c r="D46" s="5">
         <v>30</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5">
-        <v>8</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C46" s="5">
-        <v>2</v>
-      </c>
-      <c r="D46" s="5">
-        <v>1</v>
-      </c>
       <c r="E46" s="5" t="s">
-        <v>34</v>
+        <v>137</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="C47" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>256</v>
+        <v>12</v>
       </c>
       <c r="C48" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="5">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -4731,21 +4930,21 @@
         <v>8</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="C50" s="5">
         <v>1</v>
@@ -4754,88 +4953,85 @@
         <v>8</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" s="5">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5">
+        <v>8</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5">
+        <v>8</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F52" t="s">
         <v>110</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C51" s="5">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5">
-        <v>8</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F51" s="5" t="s">
+      <c r="G52" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C53" s="5">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5">
+        <v>8</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1</v>
-      </c>
-      <c r="D52" s="5">
-        <v>8</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="5">
-        <v>2</v>
-      </c>
-      <c r="D53" s="5">
-        <v>1</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="G53" s="6" t="s">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
@@ -4844,197 +5040,197 @@
         <v>8</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C55" s="5">
         <v>2</v>
       </c>
       <c r="D55" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C56" s="5">
+        <v>2</v>
+      </c>
+      <c r="D56" s="5">
+        <v>9</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F56" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="5">
-        <v>2</v>
-      </c>
-      <c r="D56" s="5">
-        <v>10</v>
-      </c>
-      <c r="E56" s="5" t="s">
+      <c r="G56" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="5">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5">
+        <v>8</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5">
+        <v>8</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" s="5">
+        <v>2</v>
+      </c>
+      <c r="D59" s="5">
+        <v>7</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" s="5">
-        <v>2</v>
-      </c>
-      <c r="D57" s="5">
-        <v>10</v>
-      </c>
-      <c r="E57" s="5" t="s">
+      <c r="G59" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C60" s="5">
+        <v>2</v>
+      </c>
+      <c r="D60" s="5">
+        <v>7</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F60" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="5">
-        <v>2</v>
-      </c>
-      <c r="D58" s="5">
-        <v>30</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F58" s="5" t="s">
+      <c r="G60" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5">
+        <v>8</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C62" s="5">
+        <v>2</v>
+      </c>
+      <c r="D62" s="5">
+        <v>25</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F62" t="s">
         <v>29</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" s="5">
-        <v>2</v>
-      </c>
-      <c r="D59" s="5">
-        <v>16</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="50" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="5">
-        <v>2</v>
-      </c>
-      <c r="D60" s="5">
-        <v>30</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C61" s="5">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5">
-        <v>8</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="5">
-        <v>1</v>
-      </c>
-      <c r="D62" s="5">
-        <v>8</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="G62" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>190</v>
+        <v>61</v>
       </c>
       <c r="C63" s="5">
         <v>1</v>
@@ -5043,41 +5239,41 @@
         <v>8</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>297</v>
+      <c r="B64" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="C64" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="F64" t="s">
-        <v>110</v>
+        <v>286</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>195</v>
+      <c r="B65" s="19" t="s">
+        <v>208</v>
       </c>
       <c r="C65" s="5">
         <v>1</v>
@@ -5086,21 +5282,21 @@
         <v>8</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>109</v>
+      <c r="B66" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="C66" s="5">
         <v>1</v>
@@ -5109,21 +5305,21 @@
         <v>8</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>116</v>
+      <c r="B67" s="19" t="s">
+        <v>123</v>
       </c>
       <c r="C67" s="5">
         <v>1</v>
@@ -5132,21 +5328,21 @@
         <v>8</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>279</v>
+        <v>111</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>231</v>
+      <c r="B68" s="19" t="s">
+        <v>203</v>
       </c>
       <c r="C68" s="5">
         <v>1</v>
@@ -5155,64 +5351,64 @@
         <v>8</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>269</v>
+        <v>32</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>266</v>
+      <c r="B69" s="19" t="s">
+        <v>141</v>
       </c>
       <c r="C69" s="5">
         <v>2</v>
       </c>
       <c r="D69" s="5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>296</v>
+      <c r="B70" s="19" t="s">
+        <v>223</v>
       </c>
       <c r="C70" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>244</v>
+      <c r="B71" s="19" t="s">
+        <v>50</v>
       </c>
       <c r="C71" s="5">
         <v>1</v>
@@ -5221,21 +5417,21 @@
         <v>8</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>27</v>
+      <c r="B72" s="19" t="s">
+        <v>90</v>
       </c>
       <c r="C72" s="5">
         <v>1</v>
@@ -5244,194 +5440,200 @@
         <v>8</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>110</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>95</v>
+      <c r="B73" s="19" t="s">
+        <v>252</v>
       </c>
       <c r="C73" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
       <c r="F73" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C74" s="5">
+        <v>2</v>
+      </c>
+      <c r="D74" s="5">
+        <v>2</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="5">
+        <v>2</v>
+      </c>
+      <c r="D75" s="5">
+        <v>1</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A76" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C76" s="5">
+        <v>2</v>
+      </c>
+      <c r="D76" s="5">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="5">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5">
+        <v>8</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="50" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C74" s="5">
-        <v>1</v>
-      </c>
-      <c r="D74" s="5">
-        <v>8</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C75" s="5">
-        <v>2</v>
-      </c>
-      <c r="D75" s="5">
+      <c r="G77" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78" s="5">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5">
+        <v>8</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C79" s="5">
+        <v>1</v>
+      </c>
+      <c r="D79" s="5">
+        <v>8</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G79" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C76" s="5">
-        <v>2</v>
-      </c>
-      <c r="D76" s="5">
-        <v>7</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C77" s="5">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5">
-        <v>8</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H77" s="7"/>
-    </row>
-    <row r="78" spans="1:8" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C78" s="5">
-        <v>2</v>
-      </c>
-      <c r="D78" s="5">
-        <v>25</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="F78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B79" s="5" t="s">
+      <c r="H79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A80" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="C79" s="5">
-        <v>1</v>
-      </c>
-      <c r="D79" s="5">
-        <v>8</v>
-      </c>
-      <c r="E79" s="5" t="s">
+      <c r="C80" s="5">
+        <v>1</v>
+      </c>
+      <c r="D80" s="5">
+        <v>8</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G80" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="H79" s="7"/>
-    </row>
-    <row r="80" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C80" s="5">
-        <v>1</v>
-      </c>
-      <c r="D80" s="5">
-        <v>8</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="19" t="s">
         <v>217</v>
       </c>
       <c r="C81" s="5">
@@ -5448,6 +5650,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G81" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G81">
+      <sortCondition sortBy="cellColor" ref="B1:B81" dxfId="1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -5455,20 +5662,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="5" max="5" width="44.7265625" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="54.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="44.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="54.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -5491,7 +5698,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>76</v>
       </c>
@@ -5514,7 +5721,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>76</v>
       </c>
@@ -5534,7 +5741,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>76</v>
       </c>
@@ -5557,7 +5764,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>76</v>
       </c>
@@ -5577,7 +5784,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>76</v>
       </c>
@@ -5597,7 +5804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -5617,7 +5824,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>76</v>
       </c>
@@ -5640,7 +5847,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>76</v>
       </c>
@@ -5663,7 +5870,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>76</v>
       </c>
@@ -5686,7 +5893,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
@@ -5706,7 +5913,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
@@ -5726,7 +5933,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>76</v>
       </c>
@@ -5749,7 +5956,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>76</v>
       </c>
@@ -5772,7 +5979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
@@ -5792,7 +5999,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>76</v>
       </c>
@@ -5815,7 +6022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
@@ -5838,7 +6045,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>76</v>
       </c>
@@ -5861,7 +6068,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>76</v>
       </c>
@@ -5884,7 +6091,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>76</v>
       </c>
@@ -5904,7 +6111,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
@@ -5935,20 +6142,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="86.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="54.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="86.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -5971,7 +6178,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>208</v>
       </c>
@@ -5994,7 +6201,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>208</v>
       </c>
@@ -6014,7 +6221,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>208</v>
       </c>
@@ -6034,7 +6241,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>208</v>
       </c>
@@ -6057,7 +6264,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>208</v>
       </c>
@@ -6080,7 +6287,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>208</v>
       </c>
@@ -6100,7 +6307,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>208</v>
       </c>
@@ -6120,7 +6327,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>208</v>
       </c>
@@ -6143,7 +6350,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>208</v>
       </c>
@@ -6163,7 +6370,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>208</v>
       </c>
@@ -6184,7 +6391,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>208</v>
       </c>
@@ -6207,7 +6414,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>208</v>
       </c>
@@ -6227,7 +6434,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>208</v>
       </c>
@@ -6247,7 +6454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>208</v>
       </c>
@@ -6267,7 +6474,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>208</v>
       </c>
@@ -6287,7 +6494,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>208</v>
       </c>
@@ -6310,7 +6517,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>208</v>
       </c>
@@ -6333,7 +6540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>208</v>
       </c>
@@ -6353,7 +6560,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>208</v>
       </c>
@@ -6376,7 +6583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>208</v>
       </c>
@@ -6396,7 +6603,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>208</v>
       </c>
@@ -6416,7 +6623,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>208</v>
       </c>
@@ -6436,7 +6643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>208</v>
       </c>
@@ -6456,7 +6663,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>208</v>
       </c>
@@ -6476,7 +6683,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>208</v>
       </c>
@@ -6496,7 +6703,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>208</v>
       </c>
@@ -6516,7 +6723,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>208</v>
       </c>
@@ -6536,7 +6743,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>208</v>
       </c>
@@ -6557,7 +6764,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>208</v>
       </c>
@@ -6585,21 +6792,21 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="6.1796875" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="5" max="5" width="48.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="48.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
     <col min="7" max="7" width="90" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -6623,7 +6830,7 @@
       </c>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>67</v>
       </c>
@@ -6647,7 +6854,7 @@
       </c>
       <c r="H2" s="9"/>
     </row>
-    <row r="3" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>67</v>
       </c>
@@ -6670,7 +6877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
@@ -6691,7 +6898,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" ht="337.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="344.25" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
@@ -6714,7 +6921,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="362.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="369.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
@@ -6734,7 +6941,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -6757,7 +6964,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>67</v>
       </c>
@@ -6777,7 +6984,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>67</v>
       </c>
@@ -6797,7 +7004,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>67</v>
       </c>
@@ -6818,7 +7025,7 @@
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>67</v>
       </c>
@@ -6841,7 +7048,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>67</v>
       </c>
@@ -6862,7 +7069,7 @@
       </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>67</v>
       </c>
@@ -6885,7 +7092,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>67</v>
       </c>
@@ -6908,7 +7115,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>67</v>
       </c>
@@ -6931,7 +7138,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>67</v>
       </c>
@@ -6952,7 +7159,7 @@
       </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>67</v>
       </c>
@@ -6972,7 +7179,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>67</v>
       </c>
@@ -6992,7 +7199,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>67</v>
       </c>
@@ -7012,7 +7219,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>67</v>
       </c>
@@ -7032,7 +7239,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>67</v>
       </c>
@@ -7055,7 +7262,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>67</v>
       </c>
@@ -7078,7 +7285,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>67</v>
       </c>
@@ -7101,7 +7308,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>67</v>
       </c>
@@ -7124,7 +7331,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>67</v>
       </c>
@@ -7147,7 +7354,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>67</v>
       </c>
@@ -7170,7 +7377,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="162.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>67</v>
       </c>
@@ -7193,7 +7400,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>67</v>
       </c>
@@ -7214,7 +7421,7 @@
       </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>67</v>
       </c>
@@ -7235,7 +7442,7 @@
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>67</v>
       </c>
@@ -7258,7 +7465,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>67</v>
       </c>
@@ -7282,7 +7489,7 @@
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>67</v>
       </c>
@@ -7306,7 +7513,7 @@
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>67</v>
       </c>
@@ -7327,7 +7534,7 @@
       </c>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>67</v>
       </c>
@@ -7349,7 +7556,7 @@
       </c>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>67</v>
       </c>
@@ -7372,7 +7579,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="162.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>67</v>
       </c>
@@ -7395,7 +7602,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>67</v>
       </c>
@@ -7418,7 +7625,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>67</v>
       </c>
@@ -7441,7 +7648,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="137.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>67</v>
       </c>
@@ -7462,7 +7669,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>67</v>
       </c>
@@ -7482,7 +7689,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>67</v>
       </c>
@@ -7503,7 +7710,7 @@
       </c>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>67</v>
       </c>
@@ -7523,7 +7730,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>67</v>
       </c>
@@ -7543,7 +7750,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>67</v>
       </c>
@@ -7563,7 +7770,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>67</v>
       </c>
@@ -7583,7 +7790,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>67</v>
       </c>
@@ -7606,7 +7813,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>67</v>
       </c>
@@ -7629,7 +7836,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>67</v>
       </c>
@@ -7652,7 +7859,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>67</v>
       </c>
@@ -7675,7 +7882,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>67</v>
       </c>
@@ -7695,7 +7902,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>67</v>
       </c>
@@ -7719,7 +7926,7 @@
       </c>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>67</v>
       </c>
@@ -7743,7 +7950,7 @@
       </c>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>67</v>
       </c>
@@ -7766,7 +7973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>67</v>
       </c>
@@ -7789,7 +7996,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>67</v>
       </c>
@@ -7812,7 +8019,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>67</v>
       </c>
@@ -7835,7 +8042,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>67</v>
       </c>
@@ -7855,7 +8062,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>67</v>
       </c>
@@ -7875,7 +8082,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>67</v>
       </c>
@@ -7898,7 +8105,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>67</v>
       </c>
@@ -7918,7 +8125,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>67</v>
       </c>
@@ -7938,7 +8145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>67</v>
       </c>
@@ -7961,7 +8168,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>67</v>
       </c>
@@ -7984,7 +8191,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>67</v>
       </c>
@@ -8007,7 +8214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>67</v>
       </c>
@@ -8030,7 +8237,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>67</v>
       </c>
@@ -8050,7 +8257,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -8073,7 +8280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>67</v>
       </c>
@@ -8096,7 +8303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>67</v>
       </c>
@@ -8119,7 +8326,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>67</v>
       </c>
@@ -8139,7 +8346,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>67</v>
       </c>
@@ -8162,7 +8369,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>67</v>
       </c>
@@ -8185,7 +8392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>67</v>
       </c>
@@ -8206,7 +8413,7 @@
       </c>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>67</v>
       </c>
@@ -8227,7 +8434,7 @@
       </c>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>67</v>
       </c>
@@ -8247,7 +8454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>67</v>
       </c>
@@ -8275,441 +8482,438 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="8.7265625" style="18"/>
-    <col min="5" max="5" width="50.81640625" style="19" customWidth="1"/>
-    <col min="6" max="6" width="41" style="18" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="18"/>
+    <col min="1" max="1" width="16.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.7109375" style="15"/>
+    <col min="5" max="5" width="50.85546875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="41" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="15" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="B2" s="18">
-        <v>2</v>
-      </c>
-      <c r="C2" s="18">
+      <c r="B2" s="15">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15">
         <v>64</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="B3" s="18">
-        <v>1</v>
-      </c>
-      <c r="C3" s="18">
-        <v>8</v>
-      </c>
-      <c r="E3" s="22" t="s">
+      <c r="B3" s="15">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="16" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:6" ht="90" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="18">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18">
-        <v>8</v>
-      </c>
-      <c r="E4" s="22" t="s">
+      <c r="B4" s="15">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="16" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="275.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:6" ht="285" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="B5" s="18">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18">
-        <v>8</v>
-      </c>
-      <c r="E5" s="22" t="s">
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="15">
+        <v>8</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="17" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="18">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18">
-        <v>8</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="B6" s="15">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15">
+        <v>8</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="B7" s="18">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18">
-        <v>8</v>
-      </c>
-      <c r="E7" s="19" t="s">
+      <c r="B7" s="15">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="17" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="145" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:6" ht="150" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="18">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18">
-        <v>8</v>
-      </c>
-      <c r="E8" s="19" t="s">
+      <c r="B8" s="15">
+        <v>1</v>
+      </c>
+      <c r="C8" s="15">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="17" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="72.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:6" ht="75" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="B9" s="18">
-        <v>1</v>
-      </c>
-      <c r="C9" s="18">
-        <v>8</v>
-      </c>
-      <c r="E9" s="19" t="s">
+      <c r="B9" s="15">
+        <v>1</v>
+      </c>
+      <c r="C9" s="15">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="17" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.2">
+      <c r="A10" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="B10" s="18">
-        <v>1</v>
-      </c>
-      <c r="C10" s="18">
-        <v>8</v>
-      </c>
-      <c r="E10" s="19" t="s">
+      <c r="B10" s="15">
+        <v>1</v>
+      </c>
+      <c r="C10" s="15">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="17" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="B11" s="18">
-        <v>1</v>
-      </c>
-      <c r="C11" s="18">
-        <v>8</v>
-      </c>
-      <c r="E11" s="19" t="s">
+      <c r="B11" s="15">
+        <v>1</v>
+      </c>
+      <c r="C11" s="15">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A12" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="B12" s="18">
-        <v>1</v>
-      </c>
-      <c r="C12" s="18">
-        <v>8</v>
-      </c>
-      <c r="E12" s="19" t="s">
+      <c r="B12" s="15">
+        <v>1</v>
+      </c>
+      <c r="C12" s="15">
+        <v>8</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:6" ht="90" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="B13" s="18">
-        <v>1</v>
-      </c>
-      <c r="C13" s="18">
-        <v>8</v>
-      </c>
-      <c r="E13" s="19" t="s">
+      <c r="B13" s="15">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15">
+        <v>8</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="17" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A14" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="B14" s="18">
-        <v>1</v>
-      </c>
-      <c r="C14" s="18">
-        <v>8</v>
-      </c>
-      <c r="E14" s="19" t="s">
+      <c r="B14" s="15">
+        <v>1</v>
+      </c>
+      <c r="C14" s="15">
+        <v>8</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A15" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="B15" s="18">
-        <v>1</v>
-      </c>
-      <c r="C15" s="18">
-        <v>8</v>
-      </c>
-      <c r="E15" s="19" t="s">
+      <c r="B15" s="15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="15">
+        <v>8</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="B16" s="18">
-        <v>1</v>
-      </c>
-      <c r="C16" s="18">
-        <v>8</v>
-      </c>
-      <c r="E16" s="19" t="s">
+      <c r="B16" s="15">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15">
+        <v>8</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="B17" s="18">
-        <v>1</v>
-      </c>
-      <c r="C17" s="18">
-        <v>8</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="B17" s="15">
+        <v>1</v>
+      </c>
+      <c r="C17" s="15">
+        <v>8</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A18" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="B18" s="18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="18">
-        <v>8</v>
-      </c>
-      <c r="E18" s="19" t="s">
+      <c r="B18" s="15">
+        <v>1</v>
+      </c>
+      <c r="C18" s="15">
+        <v>8</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A19" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="B19" s="18">
-        <v>1</v>
-      </c>
-      <c r="C19" s="18">
-        <v>8</v>
-      </c>
-      <c r="E19" s="19" t="s">
+      <c r="B19" s="15">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15">
+        <v>8</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A20" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="B20" s="18">
-        <v>1</v>
-      </c>
-      <c r="C20" s="18">
-        <v>8</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="B20" s="15">
+        <v>1</v>
+      </c>
+      <c r="C20" s="15">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="17" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+    <row r="21" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="B21" s="18">
-        <v>1</v>
-      </c>
-      <c r="C21" s="18">
-        <v>8</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="B21" s="15">
+        <v>1</v>
+      </c>
+      <c r="C21" s="15">
+        <v>8</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="15" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+    <row r="22" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="B22" s="18">
-        <v>1</v>
-      </c>
-      <c r="C22" s="18">
-        <v>8</v>
-      </c>
-      <c r="E22" s="22" t="s">
+      <c r="B22" s="15">
+        <v>1</v>
+      </c>
+      <c r="C22" s="15">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="15" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+    <row r="23" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="B23" s="18">
-        <v>1</v>
-      </c>
-      <c r="C23" s="18">
-        <v>8</v>
-      </c>
-      <c r="E23" s="22" t="s">
+      <c r="B23" s="15">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15">
+        <v>8</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="B24" s="18">
-        <v>1</v>
-      </c>
-      <c r="C24" s="18">
-        <v>8</v>
-      </c>
-      <c r="E24" s="22" t="s">
+      <c r="B24" s="15">
+        <v>1</v>
+      </c>
+      <c r="C24" s="15">
+        <v>8</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B25" s="18">
-        <v>1</v>
-      </c>
-      <c r="C25" s="18">
-        <v>8</v>
-      </c>
-      <c r="E25" s="22" t="s">
+      <c r="B25" s="15">
+        <v>1</v>
+      </c>
+      <c r="C25" s="15">
+        <v>8</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F25" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8717,271 +8921,269 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="8.7265625" style="18"/>
-    <col min="5" max="5" width="34.7265625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="38" style="18" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="18"/>
+    <col min="1" max="1" width="16.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.7109375" style="15"/>
+    <col min="5" max="5" width="34.7109375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="38" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="B2" s="18">
-        <v>2</v>
-      </c>
-      <c r="C2" s="18">
+      <c r="B2" s="15">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15">
         <v>64</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="F2" s="25"/>
-    </row>
-    <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B3" s="18">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
-        <v>8</v>
-      </c>
-      <c r="E3" s="22" t="s">
+      <c r="B3" s="15">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="16" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="B4" s="18">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18">
-        <v>8</v>
-      </c>
-      <c r="E4" s="22" t="s">
+      <c r="B4" s="15">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="16" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="275.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:6" ht="285" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="B5" s="18">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18">
-        <v>8</v>
-      </c>
-      <c r="E5" s="22" t="s">
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="15">
+        <v>8</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="17" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="18">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18">
-        <v>8</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="B6" s="15">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15">
+        <v>8</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="B7" s="18">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18">
-        <v>8</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="B7" s="15">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="18" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="B8" s="18">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18">
-        <v>8</v>
-      </c>
-      <c r="E8" s="22" t="s">
+      <c r="B8" s="15">
+        <v>1</v>
+      </c>
+      <c r="C8" s="15">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="16" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="B9" s="18">
-        <v>1</v>
-      </c>
-      <c r="C9" s="18">
-        <v>8</v>
-      </c>
-      <c r="E9" s="22" t="s">
+      <c r="B9" s="15">
+        <v>1</v>
+      </c>
+      <c r="C9" s="15">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="17" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="72.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.2">
+      <c r="A10" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B10" s="18">
-        <v>1</v>
-      </c>
-      <c r="C10" s="18">
-        <v>8</v>
-      </c>
-      <c r="E10" s="20" t="s">
+      <c r="B10" s="15">
+        <v>1</v>
+      </c>
+      <c r="C10" s="15">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="17" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="B11" s="18">
-        <v>1</v>
-      </c>
-      <c r="C11" s="18">
-        <v>8</v>
-      </c>
-      <c r="E11" s="22" t="s">
+      <c r="B11" s="15">
+        <v>1</v>
+      </c>
+      <c r="C11" s="15">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="17" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="B12" s="18">
-        <v>1</v>
-      </c>
-      <c r="C12" s="18">
-        <v>8</v>
-      </c>
-      <c r="E12" s="22" t="s">
+      <c r="B12" s="15">
+        <v>1</v>
+      </c>
+      <c r="C12" s="15">
+        <v>8</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="17" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="B13" s="18">
-        <v>1</v>
-      </c>
-      <c r="C13" s="18">
-        <v>8</v>
-      </c>
-      <c r="E13" s="22" t="s">
+      <c r="B13" s="15">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15">
+        <v>8</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="17" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="B14" s="18">
-        <v>1</v>
-      </c>
-      <c r="C14" s="18">
-        <v>8</v>
-      </c>
-      <c r="E14" s="22" t="s">
+      <c r="B14" s="15">
+        <v>1</v>
+      </c>
+      <c r="C14" s="15">
+        <v>8</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="7" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B15" s="18">
-        <v>1</v>
-      </c>
-      <c r="C15" s="18">
-        <v>8</v>
-      </c>
-      <c r="E15" s="20" t="s">
+      <c r="B15" s="15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="15">
+        <v>8</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F15" s="24"/>
+      <c r="F15" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
